--- a/sample_bank_vipiska.xlsx
+++ b/sample_bank_vipiska.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -493,7 +493,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Davr: 01.10.2026 — 15.10.2026</t>
+          <t>Davr: 01.10.2026 — 16.10.2026</t>
         </is>
       </c>
     </row>
@@ -857,16 +857,250 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="C15" s="4" t="n">
+        <v>2450000</v>
+      </c>
+      <c r="D15" s="4" t="n"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>DAVLAT G'AZNACHILIGI (SOLIQ TO'LOVLARI)</t>
+        </is>
+      </c>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>200999001</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>00014</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>23402000300100001010</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>~2001108601262903212160093~200999001~36 Ijtimoiy soliq uchun to'lov sentabr 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="C16" s="4" t="n">
+        <v>3120000</v>
+      </c>
+      <c r="D16" s="4" t="n"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>DAVLAT G'AZNACHILIGI (SOLIQ TO'LOVLARI)</t>
+        </is>
+      </c>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>200999001</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>00014</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="inlineStr">
+        <is>
+          <t>23402000300100001010</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>~1000218604262903111103093~200999001~46 Jismoniy shaxslar daromad solig'i uchun to'lov sentabr 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="n">
+        <v>31200</v>
+      </c>
+      <c r="D17" s="4" t="n"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>DAVLAT G'AZNACHILIGI (SOLIQ TO'LOVLARI)</t>
+        </is>
+      </c>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>200999001</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>00014</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="inlineStr">
+        <is>
+          <t>23402000300100001010</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>101 Jamg'arib boriladigan pensiya badali (INPS) uchun to'lov sentabr 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="n"/>
+      <c r="D18" s="4" t="n">
+        <v>4870000</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>ATB "NAMUNA BANK"</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>207000001</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>00873</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>16103000900000873001</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Humo/Uzcard terminal orqali savdo tushumi 15.10.2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>18600000</v>
+      </c>
+      <c r="D19" s="4" t="n"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>ATB "NAMUNA BANK"</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>207000001</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>00873</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
+        <is>
+          <t>16103000900000873001</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Oktyabr oyi uchun ish haqi plastik kartalarga o'tkazish</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>2000000</v>
+      </c>
+      <c r="D20" s="4" t="n"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>ATB "NAMUNA BANK"</t>
+        </is>
+      </c>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>207000001</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>00873</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="inlineStr">
+        <is>
+          <t>16103000900000873001</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Korporativ kartani (KPK) to'ldirish</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>Jami</t>
         </is>
       </c>
-      <c r="C15" s="7" t="n">
-        <v>88875000</v>
-      </c>
-      <c r="D15" s="7" t="n">
-        <v>126650000</v>
+      <c r="C21" s="7" t="n">
+        <v>115076200</v>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>131520000</v>
       </c>
     </row>
   </sheetData>
